--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_valparaiso.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:01</t>
+    <t xml:space="preserve">2026-09-09 19:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_valparaiso.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:34</t>
+    <t xml:space="preserve">2026-09-16 16:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_valparaiso.xlsx
@@ -6,29 +6,32 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sexo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comunas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Edades'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comunas'!$A$1:$D$39</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">Categoría</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saldo migratorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+  <si>
+    <t xml:space="preserve">Cambiaron de comuna dentro de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cruzaron el límite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llegaron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se fueron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la región</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -40,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16 16:33</t>
+    <t xml:space="preserve">2026-09-30 09:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -58,31 +61,145 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">M_SALDOMIGR_a</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Región de Valparaíso</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Tramo de edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 a 4 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 a 14 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 a 29 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 a 59 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 años o más</t>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras regiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras comunas de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Tabo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cartagena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Pascua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Fernández</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hijuelas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
 </sst>
 </file>
@@ -447,8 +564,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,25 +578,35 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="n">
+        <v>86513</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>13587</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>11564</v>
+        <v>125139</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>75145</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>49994</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>25151</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -493,58 +623,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -558,60 +688,560 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>602</v>
+        <v>839</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2171</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3010</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2154</v>
+        <v>1482</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1252</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2734</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4787</v>
+        <v>742</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1414</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13870</v>
+        <v>1630</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>-43</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1587</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3738</v>
+        <v>1293</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>669</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>697</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>678</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1105</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>523</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>729</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>677</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1119</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>-123</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>708</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>-441</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3203</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>-2357</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>816</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>-97</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>-66</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>744</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>-244</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>412</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>-12</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>-53</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>-252</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>-131</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>-204</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>-169</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>-288</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>-235</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>-485</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>-324</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>-1038</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>-444</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>-1062</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>-780</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1411</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>-4242</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>-2831</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:D39"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_valparaiso.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_valparaiso.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 09:52</t>
+    <t xml:space="preserve">2026-10-05 03:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
